--- a/834_issuer_etl/assets/64357/excel/cleaned_enrollees_64357.xlsx
+++ b/834_issuer_etl/assets/64357/excel/cleaned_enrollees_64357.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enrollees" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="enrollees" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,277 +429,277 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>issuer_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>isa09</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>isa10</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>isa13</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>gs04</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>gs05</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>gs06</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>st02</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>action_code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>insurer_tax_id_number</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>qtyn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>qtyy</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>qtyt</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>subscriber_flag</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>relationship_code</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>event_type_code</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>event_reason_code</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>exchg_subscriber_identifier</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>exchg_assigned_policy_id</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>exchg_indiv_identifier</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>issuer_subscriber_identifier</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>issuer_indiv_identifier</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>member_maint_effective_date</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>member_entity_identifier_code</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>member_gender_code</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>member_marital_status_code</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>member_citizenship_status_code</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>member_tobacco_usage_code</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>city</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>member_birth_date</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>maintenance_type_code</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>insurance_type_code</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>benefit_effective_begin_date</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>last_premium_paid_date</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>household_or_employee_case_id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>class_of_contract_code</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>health_coverage_policy_no</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>aptc_amt</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>health_coverage_premium_amt</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>rating_area</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>total_indiv_responsibility_amt</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>total_premium_amt</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>source_exchg_id</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>additional_maint_reason_code</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>load_timestamp</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>file_date</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>member_first_name</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>member_last_name</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>member_ssn</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>member_primary_phone_no</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>member_preferred_email</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>member_full_address</t>
         </is>
@@ -913,7 +925,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1172,7 +1184,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1431,7 +1443,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -1690,7 +1702,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -1931,7 +1943,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -2190,7 +2202,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2449,7 +2461,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -2708,7 +2720,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2967,7 +2979,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3226,7 +3238,7 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
@@ -3485,7 +3497,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -3744,7 +3756,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -4003,7 +4015,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -4262,7 +4274,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -4503,7 +4515,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -4744,7 +4756,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -4985,7 +4997,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -5226,7 +5238,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -5485,7 +5497,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -5744,7 +5756,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -6003,7 +6015,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -6262,7 +6274,7 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
@@ -6521,7 +6533,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -6780,7 +6792,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -7039,7 +7051,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -7298,7 +7310,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -7557,7 +7569,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -7816,7 +7828,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -8075,7 +8087,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -8316,7 +8328,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -8575,7 +8587,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -8834,7 +8846,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -9093,7 +9105,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -9352,7 +9364,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -9611,7 +9623,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -9870,7 +9882,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -10129,7 +10141,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -10370,7 +10382,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -10629,7 +10641,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -10888,7 +10900,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -11147,7 +11159,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -11406,7 +11418,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -11647,7 +11659,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -11888,7 +11900,7 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
@@ -12147,7 +12159,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -12406,7 +12418,7 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -12647,7 +12659,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -12888,7 +12900,7 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -13129,7 +13141,7 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -13388,7 +13400,7 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
@@ -13629,7 +13641,7 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -13888,7 +13900,7 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -14129,7 +14141,7 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
@@ -14388,7 +14400,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -14647,7 +14659,7 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
@@ -14888,7 +14900,7 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -15147,7 +15159,7 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -15406,7 +15418,7 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -15665,7 +15677,7 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -15906,7 +15918,7 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -16165,7 +16177,7 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -16424,7 +16436,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -16665,7 +16677,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -16924,7 +16936,7 @@
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
@@ -17183,7 +17195,7 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
@@ -17442,7 +17454,7 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
@@ -17701,7 +17713,7 @@
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
@@ -17960,7 +17972,7 @@
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
@@ -18201,7 +18213,7 @@
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
@@ -18460,7 +18472,7 @@
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
@@ -18719,7 +18731,7 @@
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
@@ -18960,7 +18972,7 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
@@ -19201,7 +19213,7 @@
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
@@ -19460,7 +19472,7 @@
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
@@ -19719,7 +19731,7 @@
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
@@ -19978,7 +19990,7 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -20237,7 +20249,7 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
@@ -20496,7 +20508,7 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
@@ -20755,7 +20767,7 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
@@ -20996,7 +21008,7 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
@@ -21237,7 +21249,7 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
@@ -21478,7 +21490,7 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
@@ -21737,7 +21749,7 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
@@ -21996,7 +22008,7 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
@@ -22237,7 +22249,7 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
@@ -22496,7 +22508,7 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
@@ -22755,7 +22767,7 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
@@ -23014,7 +23026,7 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
@@ -23273,7 +23285,7 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
@@ -23532,7 +23544,7 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
@@ -23773,7 +23785,7 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -24032,7 +24044,7 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
@@ -24291,7 +24303,7 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
@@ -24550,7 +24562,7 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
@@ -24791,7 +24803,7 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
@@ -25032,7 +25044,7 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -25291,7 +25303,7 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
@@ -25532,7 +25544,7 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
@@ -25773,7 +25785,7 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
@@ -26032,7 +26044,7 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
@@ -26291,7 +26303,7 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
@@ -26550,7 +26562,7 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
@@ -26809,7 +26821,7 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
@@ -27068,7 +27080,7 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
@@ -27327,7 +27339,7 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
@@ -27586,7 +27598,7 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
@@ -27845,7 +27857,7 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
@@ -28104,7 +28116,7 @@
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
@@ -28363,7 +28375,7 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
@@ -28622,7 +28634,7 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
@@ -28863,7 +28875,7 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
@@ -29122,7 +29134,7 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
@@ -29363,7 +29375,7 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
@@ -29622,7 +29634,7 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
@@ -29881,7 +29893,7 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
@@ -30140,7 +30152,7 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
@@ -30381,7 +30393,7 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
@@ -30640,7 +30652,7 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
@@ -30899,7 +30911,7 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
@@ -31140,7 +31152,7 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
@@ -31399,7 +31411,7 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
@@ -31658,7 +31670,7 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
@@ -31917,7 +31929,7 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
@@ -32158,7 +32170,7 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
@@ -32417,7 +32429,7 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
@@ -32676,7 +32688,7 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
@@ -32917,7 +32929,7 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
@@ -33158,7 +33170,7 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
@@ -33417,7 +33429,7 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
@@ -33676,7 +33688,7 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
@@ -33935,7 +33947,7 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
@@ -34194,7 +34206,7 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
@@ -34453,7 +34465,7 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
@@ -34712,7 +34724,7 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
@@ -34971,7 +34983,7 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
@@ -35230,7 +35242,7 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
@@ -35489,7 +35501,7 @@
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
@@ -35748,7 +35760,7 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
@@ -35989,7 +36001,7 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
@@ -36230,7 +36242,7 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
@@ -36489,7 +36501,7 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
@@ -36748,7 +36760,7 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
@@ -37007,7 +37019,7 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
@@ -37266,7 +37278,7 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
@@ -37525,7 +37537,7 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
@@ -37784,7 +37796,7 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
@@ -38043,7 +38055,7 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
@@ -38284,7 +38296,7 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
@@ -38543,7 +38555,7 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
@@ -38802,7 +38814,7 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>2026-06-08 03:09:15</t>
+          <t>2026-06-08 03:14:52</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
